--- a/testdata/sample_creds.xlsx
+++ b/testdata/sample_creds.xlsx
@@ -1039,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
   <cols>
     <col width="12.4545454545455" customWidth="1" min="1" max="1"/>
@@ -1057,40 +1057,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <f>SUM(A2:A6)</f>
-        <v/>
-      </c>
-    </row>
+    <row r="2" ht="17" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
